--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-Picarro.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-Picarro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6AA35B-67AE-4852-A776-C6634DBB2106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7A5DA6-C006-43C7-9BF5-9739F73E2725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-2820" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jar and valve id overview" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
     Delayed by excacly 1 h from real time</t>
       </text>
     </comment>
-    <comment ref="H8" authorId="1" shapeId="0" xr:uid="{D6A11C27-28E7-4435-BC4A-E3E1711C9750}">
+    <comment ref="I8" authorId="1" shapeId="0" xr:uid="{D6A11C27-28E7-4435-BC4A-E3E1711C9750}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="26">
   <si>
     <t>Picarro ID</t>
   </si>
@@ -136,6 +136,12 @@
   </si>
   <si>
     <t>endtime Piccarro</t>
+  </si>
+  <si>
+    <t>enddate</t>
+  </si>
+  <si>
+    <t>startdate</t>
   </si>
 </sst>
 </file>
@@ -145,19 +151,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -192,12 +192,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,7 +488,7 @@
   <threadedComment ref="F2" dT="2026-01-08T09:15:27.58" personId="{665E6C45-FDD8-469A-93B0-28134F14276F}" id="{DFE91DE2-97B6-4683-BB64-BFCD2C85D76D}">
     <text>Delayed by excacly 1 h from real time</text>
   </threadedComment>
-  <threadedComment ref="H8" dT="2026-01-08T09:23:24.74" personId="{665E6C45-FDD8-469A-93B0-28134F14276F}" id="{D6A11C27-28E7-4435-BC4A-E3E1711C9750}">
+  <threadedComment ref="I8" dT="2026-01-08T09:23:24.74" personId="{665E6C45-FDD8-469A-93B0-28134F14276F}" id="{D6A11C27-28E7-4435-BC4A-E3E1711C9750}">
     <text>Didn’t write this, using an average from other jar measurements</text>
   </threadedComment>
 </ThreadedComments>
@@ -728,7 +729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1A1D03-873D-49A4-B894-14582A5CC970}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
@@ -736,14 +737,15 @@
     <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" customWidth="1"/>
     <col min="8" max="8" width="21.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -763,22 +765,28 @@
         <v>9</v>
       </c>
       <c r="G1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -797,14 +805,29 @@
       <c r="F2" s="1">
         <v>0.42916666666666664</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="5">
+        <v>46028</v>
+      </c>
+      <c r="H2">
         <v>0.22500000000000001</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.93799999999999994</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="K2">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="M2" s="5">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -820,14 +843,20 @@
       <c r="E3">
         <v>2.1349999999999998</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.224</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.94399999999999995</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="K3">
+        <v>0.93799999999999994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -843,14 +872,20 @@
       <c r="E4">
         <v>2.0219999999999998</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.22600000000000001</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="4">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="K4">
+        <v>0.94099999999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -866,14 +901,20 @@
       <c r="E5">
         <v>2.0499999999999998</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.22600000000000001</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>0.94499999999999995</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="K5">
+        <v>0.93400000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -889,14 +930,20 @@
       <c r="E6">
         <v>2.097</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.22600000000000001</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0.94799999999999995</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="K6">
+        <v>0.93799999999999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>11</v>
       </c>
@@ -909,14 +956,20 @@
       <c r="D7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="4">
+      <c r="H7" s="4">
         <v>0.4</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0.77600000000000002</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="K7">
+        <v>0.75900000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -932,15 +985,21 @@
       <c r="E8">
         <v>2.0710000000000002</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.22700000000000001</v>
       </c>
-      <c r="H8" s="4">
-        <f>AVERAGE(H2:H6,H10:H12,H14:H18,H20:H24)</f>
+      <c r="I8" s="4">
+        <f>AVERAGE(I2:I6,I10:I12,I14:I18,I20:I24)</f>
         <v>0.9454999999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="K8">
+        <v>0.93600000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -956,14 +1015,20 @@
       <c r="E9">
         <v>2.0819999999999999</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.22500000000000001</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0.94499999999999995</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J9" s="4">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="K9">
+        <v>0.93799999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -979,14 +1044,20 @@
       <c r="E10" s="4">
         <v>2.02</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>0.22600000000000001</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>0.94399999999999995</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="K10">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1002,14 +1073,20 @@
       <c r="E11" s="4">
         <v>2.08</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.22500000000000001</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.94599999999999995</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J11">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="K11">
+        <v>0.93500000000000005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1025,14 +1102,20 @@
       <c r="E12" s="4">
         <v>2.0299999999999998</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.22600000000000001</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0.94499999999999995</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J12">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="K12">
+        <v>0.93600000000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1045,14 +1128,20 @@
       <c r="D13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.39800000000000002</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.77900000000000003</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="K13">
+        <v>0.75900000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>16</v>
       </c>
@@ -1068,14 +1157,20 @@
       <c r="E14" s="4">
         <v>2.0299999999999998</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.22700000000000001</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0.94199999999999995</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J14" s="4">
+        <v>0.23</v>
+      </c>
+      <c r="K14">
+        <v>0.94399999999999995</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>16</v>
       </c>
@@ -1091,14 +1186,20 @@
       <c r="E15" s="4">
         <v>2.1070000000000002</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.22700000000000001</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0.93899999999999995</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="K15">
+        <v>0.93400000000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -1114,14 +1215,20 @@
       <c r="E16" s="4">
         <v>2.0419999999999998</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.22700000000000001</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>0.94099999999999995</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="K16">
+        <v>0.97499999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1137,14 +1244,20 @@
       <c r="E17" s="4">
         <v>2.02</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.22600000000000001</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>0.94299999999999995</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="K17">
+        <v>0.93500000000000005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1160,14 +1273,20 @@
       <c r="E18" s="4">
         <v>2.0649999999999999</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>0.22700000000000001</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0.94299999999999995</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="K18">
+        <v>0.93500000000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1180,14 +1299,20 @@
       <c r="D19" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.443</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0.73399999999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J19">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="K19">
+        <v>0.71599999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>16</v>
       </c>
@@ -1203,14 +1328,20 @@
       <c r="E20" s="4">
         <v>2.0870000000000002</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.224</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0.99399999999999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J20">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="K20">
+        <v>0.93799999999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1226,14 +1357,20 @@
       <c r="E21" s="4">
         <v>2.0390000000000001</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.22600000000000001</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0.94299999999999995</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J21">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="K21">
+        <v>0.93300000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>16</v>
       </c>
@@ -1249,14 +1386,20 @@
       <c r="E22" s="4">
         <v>2.09</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.22600000000000001</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0.94099999999999995</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J22">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="K22">
+        <v>0.93100000000000005</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>16</v>
       </c>
@@ -1272,14 +1415,20 @@
       <c r="E23" s="4">
         <v>2.0979999999999999</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.22500000000000001</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0.94099999999999995</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J23">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="K23">
+        <v>0.93300000000000005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>16</v>
       </c>
@@ -1295,14 +1444,20 @@
       <c r="E24" s="4">
         <v>2.0859999999999999</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>0.22600000000000001</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>0.94199999999999995</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="K24">
+        <v>0.93300000000000005</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>16</v>
       </c>
@@ -1315,11 +1470,17 @@
       <c r="D25" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>0.44500000000000001</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>0.73299999999999998</v>
+      </c>
+      <c r="J25">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="K25">
+        <v>0.71499999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-Picarro.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-Picarro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7A5DA6-C006-43C7-9BF5-9739F73E2725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C09F16-E88A-470E-BCBB-02C6FCDED5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jar and valve id overview" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,8 @@
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Delayed by excacly 1 h from real time</t>
+    Real time noted
+09:17 in Picarro log-file, known delay by excatly 1 h</t>
       </text>
     </comment>
     <comment ref="I8" authorId="1" shapeId="0" xr:uid="{D6A11C27-28E7-4435-BC4A-E3E1711C9750}">
@@ -486,7 +487,8 @@
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="F2" dT="2026-01-08T09:15:27.58" personId="{665E6C45-FDD8-469A-93B0-28134F14276F}" id="{DFE91DE2-97B6-4683-BB64-BFCD2C85D76D}">
-    <text>Delayed by excacly 1 h from real time</text>
+    <text>Real time noted
+09:17 in Picarro log-file, known delay by excatly 1 h</text>
   </threadedComment>
   <threadedComment ref="I8" dT="2026-01-08T09:23:24.74" personId="{665E6C45-FDD8-469A-93B0-28134F14276F}" id="{D6A11C27-28E7-4435-BC4A-E3E1711C9750}">
     <text>Didn’t write this, using an average from other jar measurements</text>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-Picarro.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-Picarro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C09F16-E88A-470E-BCBB-02C6FCDED5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818896A0-0BBC-4E32-B9CC-D772F47913E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2988" yWindow="2100" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jar and valve id overview" sheetId="1" r:id="rId1"/>
@@ -1377,7 +1377,7 @@
         <v>16</v>
       </c>
       <c r="B22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>18</v>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-Picarro.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-Picarro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818896A0-0BBC-4E32-B9CC-D772F47913E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1841CB-BF26-4EFC-8D26-8D6080205F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2988" yWindow="2100" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jar and valve id overview" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 09:17 in Picarro log-file, known delay by excatly 1 h</t>
       </text>
     </comment>
-    <comment ref="I8" authorId="1" shapeId="0" xr:uid="{D6A11C27-28E7-4435-BC4A-E3E1711C9750}">
+    <comment ref="J8" authorId="1" shapeId="0" xr:uid="{D6A11C27-28E7-4435-BC4A-E3E1711C9750}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="27">
   <si>
     <t>Picarro ID</t>
   </si>
@@ -143,6 +143,26 @@
   </si>
   <si>
     <t>startdate</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>t [h]</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -152,13 +172,25 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -193,13 +225,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,7 +523,7 @@
     <text>Real time noted
 09:17 in Picarro log-file, known delay by excatly 1 h</text>
   </threadedComment>
-  <threadedComment ref="I8" dT="2026-01-08T09:23:24.74" personId="{665E6C45-FDD8-469A-93B0-28134F14276F}" id="{D6A11C27-28E7-4435-BC4A-E3E1711C9750}">
+  <threadedComment ref="J8" dT="2026-01-08T09:23:24.74" personId="{665E6C45-FDD8-469A-93B0-28134F14276F}" id="{D6A11C27-28E7-4435-BC4A-E3E1711C9750}">
     <text>Didn’t write this, using an average from other jar measurements</text>
   </threadedComment>
 </ThreadedComments>
@@ -731,13 +764,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1A1D03-873D-49A4-B894-14582A5CC970}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.109375" customWidth="1"/>
     <col min="8" max="8" width="21.77734375" bestFit="1" customWidth="1"/>
@@ -747,7 +780,7 @@
     <col min="13" max="13" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -760,7 +793,7 @@
       <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F1" t="s">
@@ -769,26 +802,30 @@
       <c r="G1" t="s">
         <v>25</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>22</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>23</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O1" s="6"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -801,7 +838,7 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>2.04</v>
       </c>
       <c r="F2" s="1">
@@ -811,25 +848,28 @@
         <v>46028</v>
       </c>
       <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>0.22500000000000001</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.93799999999999994</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.27400000000000002</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.89700000000000002</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>0.54861111111111116</v>
       </c>
-      <c r="M2" s="5">
+      <c r="N2" s="5">
         <v>46034</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -842,23 +882,26 @@
       <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="4">
         <v>2.1349999999999998</v>
       </c>
       <c r="H3">
+        <v>0.25</v>
+      </c>
+      <c r="I3">
         <v>0.224</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.94399999999999995</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.23300000000000001</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.93799999999999994</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -871,23 +914,27 @@
       <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>2.0219999999999998</v>
       </c>
       <c r="H4">
+        <f>H3+0.25</f>
+        <v>0.5</v>
+      </c>
+      <c r="I4">
         <v>0.22600000000000001</v>
       </c>
-      <c r="I4" s="4">
+      <c r="J4" s="4">
         <v>0.94</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.22900000000000001</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.94099999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -900,23 +947,27 @@
       <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <v>2.0499999999999998</v>
       </c>
       <c r="H5">
+        <f t="shared" ref="H5:H6" si="0">H4+0.25</f>
+        <v>0.75</v>
+      </c>
+      <c r="I5">
         <v>0.22600000000000001</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.94499999999999995</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.23599999999999999</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.93400000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -929,23 +980,27 @@
       <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <v>2.097</v>
       </c>
       <c r="H6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>0.22600000000000001</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>0.94799999999999995</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.23300000000000001</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.93799999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>11</v>
       </c>
@@ -958,20 +1013,24 @@
       <c r="D7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7">
+        <f>H6+0.5</f>
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="4">
         <v>0.4</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>0.77600000000000002</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.41899999999999998</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.75900000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -984,24 +1043,28 @@
       <c r="D8" t="s">
         <v>16</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="4">
         <v>2.0710000000000002</v>
       </c>
       <c r="H8">
+        <f>H7+0.25</f>
+        <v>1.75</v>
+      </c>
+      <c r="I8">
         <v>0.22700000000000001</v>
       </c>
-      <c r="I8" s="4">
-        <f>AVERAGE(I2:I6,I10:I12,I14:I18,I20:I24)</f>
+      <c r="J8" s="4">
+        <f>AVERAGE(J2:J6,J10:J12,J14:J18,J20:J24)</f>
         <v>0.9454999999999999</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.23400000000000001</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.93600000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1014,23 +1077,27 @@
       <c r="D9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="4">
         <v>2.0819999999999999</v>
       </c>
       <c r="H9">
+        <f t="shared" ref="H9:H12" si="1">H8+0.25</f>
+        <v>2</v>
+      </c>
+      <c r="I9">
         <v>0.22500000000000001</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>0.94499999999999995</v>
       </c>
-      <c r="J9" s="4">
+      <c r="K9" s="4">
         <v>0.23100000000000001</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.93799999999999994</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1047,19 +1114,23 @@
         <v>2.02</v>
       </c>
       <c r="H10">
+        <f t="shared" si="1"/>
+        <v>2.25</v>
+      </c>
+      <c r="I10">
         <v>0.22600000000000001</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.94399999999999995</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>0.23300000000000001</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.94</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1076,19 +1147,23 @@
         <v>2.08</v>
       </c>
       <c r="H11">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="I11">
         <v>0.22500000000000001</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>0.94599999999999995</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>0.23599999999999999</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.93500000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1105,19 +1180,23 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="H12">
+        <f t="shared" si="1"/>
+        <v>2.75</v>
+      </c>
+      <c r="I12">
         <v>0.22600000000000001</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.94499999999999995</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.23200000000000001</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.93600000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1131,19 +1210,23 @@
         <v>4</v>
       </c>
       <c r="H13">
+        <f>H12+0.5</f>
+        <v>3.25</v>
+      </c>
+      <c r="I13">
         <v>0.39800000000000002</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.77900000000000003</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.41599999999999998</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.75900000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>16</v>
       </c>
@@ -1160,19 +1243,23 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="H14">
+        <f>H13+0.25</f>
+        <v>3.5</v>
+      </c>
+      <c r="I14">
         <v>0.22700000000000001</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.94199999999999995</v>
       </c>
-      <c r="J14" s="4">
+      <c r="K14" s="4">
         <v>0.23</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.94399999999999995</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>16</v>
       </c>
@@ -1189,19 +1276,23 @@
         <v>2.1070000000000002</v>
       </c>
       <c r="H15">
+        <f t="shared" ref="H15:H18" si="2">H14+0.25</f>
+        <v>3.75</v>
+      </c>
+      <c r="I15">
         <v>0.22700000000000001</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.93899999999999995</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>0.23599999999999999</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.93400000000000005</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -1218,19 +1309,23 @@
         <v>2.0419999999999998</v>
       </c>
       <c r="H16">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="I16">
         <v>0.22700000000000001</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>0.94099999999999995</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>0.19900000000000001</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.97499999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1247,19 +1342,23 @@
         <v>2.02</v>
       </c>
       <c r="H17">
+        <f t="shared" si="2"/>
+        <v>4.25</v>
+      </c>
+      <c r="I17">
         <v>0.22600000000000001</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.94299999999999995</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>0.23599999999999999</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.93500000000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1276,19 +1375,23 @@
         <v>2.0649999999999999</v>
       </c>
       <c r="H18">
+        <f t="shared" si="2"/>
+        <v>4.5</v>
+      </c>
+      <c r="I18">
         <v>0.22700000000000001</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>0.94299999999999995</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.23599999999999999</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>0.93500000000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1302,19 +1405,23 @@
         <v>4</v>
       </c>
       <c r="H19">
+        <f>H18+0.5</f>
+        <v>5</v>
+      </c>
+      <c r="I19">
         <v>0.443</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.73399999999999999</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.46100000000000002</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.71599999999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>16</v>
       </c>
@@ -1331,19 +1438,23 @@
         <v>2.0870000000000002</v>
       </c>
       <c r="H20">
+        <f>H19+0.25</f>
+        <v>5.25</v>
+      </c>
+      <c r="I20">
         <v>0.224</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.99399999999999999</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.23300000000000001</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.93799999999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1360,19 +1471,23 @@
         <v>2.0390000000000001</v>
       </c>
       <c r="H21">
+        <f t="shared" ref="H21:H24" si="3">H20+0.25</f>
+        <v>5.5</v>
+      </c>
+      <c r="I21">
         <v>0.22600000000000001</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.94299999999999995</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.23799999999999999</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.93300000000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>16</v>
       </c>
@@ -1389,19 +1504,23 @@
         <v>2.09</v>
       </c>
       <c r="H22">
+        <f t="shared" si="3"/>
+        <v>5.75</v>
+      </c>
+      <c r="I22">
         <v>0.22600000000000001</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.94099999999999995</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.23899999999999999</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.93100000000000005</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>16</v>
       </c>
@@ -1418,19 +1537,23 @@
         <v>2.0979999999999999</v>
       </c>
       <c r="H23">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="I23">
         <v>0.22500000000000001</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.94099999999999995</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.23799999999999999</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.93300000000000005</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>16</v>
       </c>
@@ -1447,19 +1570,23 @@
         <v>2.0859999999999999</v>
       </c>
       <c r="H24">
+        <f t="shared" si="3"/>
+        <v>6.25</v>
+      </c>
+      <c r="I24">
         <v>0.22600000000000001</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>0.94199999999999995</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>0.23699999999999999</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>0.93300000000000005</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>16</v>
       </c>
@@ -1473,15 +1600,19 @@
         <v>4</v>
       </c>
       <c r="H25">
+        <f>H24+0.5</f>
+        <v>6.75</v>
+      </c>
+      <c r="I25">
         <v>0.44500000000000001</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>0.73299999999999998</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>0.46100000000000002</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>0.71499999999999997</v>
       </c>
     </row>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-Picarro.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-Picarro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1841CB-BF26-4EFC-8D26-8D6080205F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7803C917-8512-4C15-835D-C9CB7E031BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="30">
   <si>
     <t>Picarro ID</t>
   </si>
@@ -97,9 +97,6 @@
     <t>Starttime Picarro</t>
   </si>
   <si>
-    <t>Q sample end [mL/min]</t>
-  </si>
-  <si>
     <t>P Untr</t>
   </si>
   <si>
@@ -125,15 +122,6 @@
   </si>
   <si>
     <t>P Unrt</t>
-  </si>
-  <si>
-    <t>Q sample start [L/min]</t>
-  </si>
-  <si>
-    <t>Q Bypass start [L/min]</t>
-  </si>
-  <si>
-    <t>Q  Bypass end [L/min]</t>
   </si>
   <si>
     <t>endtime Piccarro</t>
@@ -163,6 +151,27 @@
       </rPr>
       <t>t [h]</t>
     </r>
+  </si>
+  <si>
+    <t>Q sample start [SL/min]</t>
+  </si>
+  <si>
+    <t>Q Bypass start [SL/min]</t>
+  </si>
+  <si>
+    <t>Q sample end [SL/min]</t>
+  </si>
+  <si>
+    <t>Q  Bypass end [SL/min]</t>
+  </si>
+  <si>
+    <t>Qtot start [SL/min]</t>
+  </si>
+  <si>
+    <t>Qtot end [SL/min]</t>
+  </si>
+  <si>
+    <t>Q mean [Sl/min]</t>
   </si>
 </sst>
 </file>
@@ -225,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -233,6 +242,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -764,7 +774,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1A1D03-873D-49A4-B894-14582A5CC970}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
@@ -778,9 +788,14 @@
     <col min="11" max="11" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.77734375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.33203125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -800,32 +815,40 @@
         <v>9</v>
       </c>
       <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="L1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="6"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -836,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="4">
         <v>2.04</v>
@@ -862,14 +885,26 @@
       <c r="L2">
         <v>0.89700000000000002</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>0.54861111111111116</v>
       </c>
-      <c r="N2" s="5">
+      <c r="O2" s="5">
         <v>46034</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P2" s="4">
+        <f>I2+J2</f>
+        <v>1.163</v>
+      </c>
+      <c r="Q2" s="4">
+        <f>K2+L2</f>
+        <v>1.171</v>
+      </c>
+      <c r="R2" s="4">
+        <f>AVERAGE(P2:Q2)</f>
+        <v>1.167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -880,7 +915,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="4">
         <v>2.1349999999999998</v>
@@ -900,8 +935,20 @@
       <c r="L3">
         <v>0.93799999999999994</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3" s="4">
+        <f t="shared" ref="P3:P25" si="0">I3+J3</f>
+        <v>1.1679999999999999</v>
+      </c>
+      <c r="Q3" s="4">
+        <f t="shared" ref="Q3:Q25" si="1">K3+L3</f>
+        <v>1.171</v>
+      </c>
+      <c r="R3" s="4">
+        <f t="shared" ref="R3:R25" si="2">AVERAGE(P3:Q3)</f>
+        <v>1.1695</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -912,7 +959,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="4">
         <v>2.0219999999999998</v>
@@ -933,8 +980,20 @@
       <c r="L4">
         <v>0.94099999999999995</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1659999999999999</v>
+      </c>
+      <c r="Q4" s="4">
+        <f t="shared" si="1"/>
+        <v>1.17</v>
+      </c>
+      <c r="R4" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1679999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -945,13 +1004,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="4">
         <v>2.0499999999999998</v>
       </c>
       <c r="H5">
-        <f t="shared" ref="H5:H6" si="0">H4+0.25</f>
+        <f t="shared" ref="H5:H6" si="3">H4+0.25</f>
         <v>0.75</v>
       </c>
       <c r="I5">
@@ -966,8 +1025,20 @@
       <c r="L5">
         <v>0.93400000000000005</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.171</v>
+      </c>
+      <c r="Q5" s="4">
+        <f t="shared" si="1"/>
+        <v>1.17</v>
+      </c>
+      <c r="R5" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1705000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -978,13 +1049,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="4">
         <v>2.097</v>
       </c>
       <c r="H6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I6">
@@ -999,8 +1070,20 @@
       <c r="L6">
         <v>0.93799999999999994</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="Q6" s="4">
+        <f t="shared" si="1"/>
+        <v>1.171</v>
+      </c>
+      <c r="R6" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1724999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>11</v>
       </c>
@@ -1029,8 +1112,20 @@
       <c r="L7">
         <v>0.75900000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1760000000000002</v>
+      </c>
+      <c r="Q7" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1779999999999999</v>
+      </c>
+      <c r="R7" s="7">
+        <f t="shared" si="2"/>
+        <v>1.177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1041,7 +1136,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="4">
         <v>2.0710000000000002</v>
@@ -1063,8 +1158,20 @@
       <c r="L8">
         <v>0.93600000000000005</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1724999999999999</v>
+      </c>
+      <c r="Q8" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1700000000000002</v>
+      </c>
+      <c r="R8" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1712500000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1075,13 +1182,13 @@
         <v>7</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" s="4">
         <v>2.0819999999999999</v>
       </c>
       <c r="H9">
-        <f t="shared" ref="H9:H12" si="1">H8+0.25</f>
+        <f t="shared" ref="H9:H12" si="4">H8+0.25</f>
         <v>2</v>
       </c>
       <c r="I9">
@@ -1096,8 +1203,20 @@
       <c r="L9">
         <v>0.93799999999999994</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P9" s="4">
+        <f t="shared" si="0"/>
+        <v>1.17</v>
+      </c>
+      <c r="Q9" s="4">
+        <f t="shared" si="1"/>
+        <v>1.169</v>
+      </c>
+      <c r="R9" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1695</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1108,13 +1227,13 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="4">
         <v>2.02</v>
       </c>
       <c r="H10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.25</v>
       </c>
       <c r="I10">
@@ -1129,8 +1248,20 @@
       <c r="L10">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P10" s="4">
+        <f t="shared" si="0"/>
+        <v>1.17</v>
+      </c>
+      <c r="Q10" s="4">
+        <f t="shared" si="1"/>
+        <v>1.173</v>
+      </c>
+      <c r="R10" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1715</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1141,13 +1272,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4">
         <v>2.08</v>
       </c>
       <c r="H11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
       <c r="I11">
@@ -1162,8 +1293,20 @@
       <c r="L11">
         <v>0.93500000000000005</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P11" s="4">
+        <f t="shared" si="0"/>
+        <v>1.171</v>
+      </c>
+      <c r="Q11" s="4">
+        <f t="shared" si="1"/>
+        <v>1.171</v>
+      </c>
+      <c r="R11" s="4">
+        <f t="shared" si="2"/>
+        <v>1.171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1174,13 +1317,13 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" s="4">
         <v>2.0299999999999998</v>
       </c>
       <c r="H12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.75</v>
       </c>
       <c r="I12">
@@ -1195,8 +1338,20 @@
       <c r="L12">
         <v>0.93600000000000005</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P12" s="4">
+        <f t="shared" si="0"/>
+        <v>1.171</v>
+      </c>
+      <c r="Q12" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1680000000000001</v>
+      </c>
+      <c r="R12" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1695000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1225,8 +1380,20 @@
       <c r="L13">
         <v>0.75900000000000001</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P13" s="4">
+        <f t="shared" si="0"/>
+        <v>1.177</v>
+      </c>
+      <c r="Q13" s="4">
+        <f t="shared" si="1"/>
+        <v>1.175</v>
+      </c>
+      <c r="R13" s="7">
+        <f t="shared" si="2"/>
+        <v>1.1760000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>16</v>
       </c>
@@ -1237,7 +1404,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="4">
         <v>2.0299999999999998</v>
@@ -1258,8 +1425,20 @@
       <c r="L14">
         <v>0.94399999999999995</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P14" s="4">
+        <f t="shared" si="0"/>
+        <v>1.169</v>
+      </c>
+      <c r="Q14" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="R14" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1715</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>16</v>
       </c>
@@ -1270,13 +1449,13 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" s="4">
         <v>2.1070000000000002</v>
       </c>
       <c r="H15">
-        <f t="shared" ref="H15:H18" si="2">H14+0.25</f>
+        <f t="shared" ref="H15:H18" si="5">H14+0.25</f>
         <v>3.75</v>
       </c>
       <c r="I15">
@@ -1291,8 +1470,20 @@
       <c r="L15">
         <v>0.93400000000000005</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P15" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1659999999999999</v>
+      </c>
+      <c r="Q15" s="4">
+        <f t="shared" si="1"/>
+        <v>1.17</v>
+      </c>
+      <c r="R15" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1679999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -1303,13 +1494,13 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" s="4">
         <v>2.0419999999999998</v>
       </c>
       <c r="H16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="I16">
@@ -1324,8 +1515,20 @@
       <c r="L16">
         <v>0.97499999999999998</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P16" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1679999999999999</v>
+      </c>
+      <c r="Q16" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1739999999999999</v>
+      </c>
+      <c r="R16" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1709999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1336,13 +1539,13 @@
         <v>14</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="4">
         <v>2.02</v>
       </c>
       <c r="H17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4.25</v>
       </c>
       <c r="I17">
@@ -1357,8 +1560,20 @@
       <c r="L17">
         <v>0.93500000000000005</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P17" s="4">
+        <f t="shared" si="0"/>
+        <v>1.169</v>
+      </c>
+      <c r="Q17" s="4">
+        <f t="shared" si="1"/>
+        <v>1.171</v>
+      </c>
+      <c r="R17" s="4">
+        <f t="shared" si="2"/>
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1369,13 +1584,13 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" s="4">
         <v>2.0649999999999999</v>
       </c>
       <c r="H18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4.5</v>
       </c>
       <c r="I18">
@@ -1390,8 +1605,20 @@
       <c r="L18">
         <v>0.93500000000000005</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P18" s="4">
+        <f t="shared" si="0"/>
+        <v>1.17</v>
+      </c>
+      <c r="Q18" s="4">
+        <f t="shared" si="1"/>
+        <v>1.171</v>
+      </c>
+      <c r="R18" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1705000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1420,8 +1647,20 @@
       <c r="L19">
         <v>0.71599999999999997</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P19" s="4">
+        <f t="shared" si="0"/>
+        <v>1.177</v>
+      </c>
+      <c r="Q19" s="4">
+        <f t="shared" si="1"/>
+        <v>1.177</v>
+      </c>
+      <c r="R19" s="7">
+        <f t="shared" si="2"/>
+        <v>1.177</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>16</v>
       </c>
@@ -1432,7 +1671,7 @@
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E20" s="4">
         <v>2.0870000000000002</v>
@@ -1453,8 +1692,20 @@
       <c r="L20">
         <v>0.93799999999999994</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P20" s="4">
+        <f t="shared" si="0"/>
+        <v>1.218</v>
+      </c>
+      <c r="Q20" s="4">
+        <f t="shared" si="1"/>
+        <v>1.171</v>
+      </c>
+      <c r="R20" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1945000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1465,13 +1716,13 @@
         <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E21" s="4">
         <v>2.0390000000000001</v>
       </c>
       <c r="H21">
-        <f t="shared" ref="H21:H24" si="3">H20+0.25</f>
+        <f t="shared" ref="H21:H24" si="6">H20+0.25</f>
         <v>5.5</v>
       </c>
       <c r="I21">
@@ -1486,8 +1737,20 @@
       <c r="L21">
         <v>0.93300000000000005</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P21" s="4">
+        <f t="shared" si="0"/>
+        <v>1.169</v>
+      </c>
+      <c r="Q21" s="4">
+        <f t="shared" si="1"/>
+        <v>1.171</v>
+      </c>
+      <c r="R21" s="4">
+        <f t="shared" si="2"/>
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>16</v>
       </c>
@@ -1498,13 +1761,13 @@
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="4">
         <v>2.09</v>
       </c>
       <c r="H22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.75</v>
       </c>
       <c r="I22">
@@ -1519,8 +1782,20 @@
       <c r="L22">
         <v>0.93100000000000005</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P22" s="4">
+        <f t="shared" si="0"/>
+        <v>1.167</v>
+      </c>
+      <c r="Q22" s="4">
+        <f t="shared" si="1"/>
+        <v>1.17</v>
+      </c>
+      <c r="R22" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1684999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>16</v>
       </c>
@@ -1531,13 +1806,13 @@
         <v>19</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E23" s="4">
         <v>2.0979999999999999</v>
       </c>
       <c r="H23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="I23">
@@ -1552,8 +1827,20 @@
       <c r="L23">
         <v>0.93300000000000005</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P23" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1659999999999999</v>
+      </c>
+      <c r="Q23" s="4">
+        <f t="shared" si="1"/>
+        <v>1.171</v>
+      </c>
+      <c r="R23" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1684999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>16</v>
       </c>
@@ -1564,13 +1851,13 @@
         <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" s="4">
         <v>2.0859999999999999</v>
       </c>
       <c r="H24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.25</v>
       </c>
       <c r="I24">
@@ -1585,8 +1872,20 @@
       <c r="L24">
         <v>0.93300000000000005</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="P24" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1679999999999999</v>
+      </c>
+      <c r="Q24" s="4">
+        <f t="shared" si="1"/>
+        <v>1.17</v>
+      </c>
+      <c r="R24" s="4">
+        <f t="shared" si="2"/>
+        <v>1.169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>16</v>
       </c>
@@ -1614,6 +1913,18 @@
       </c>
       <c r="L25">
         <v>0.71499999999999997</v>
+      </c>
+      <c r="P25" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1779999999999999</v>
+      </c>
+      <c r="Q25" s="4">
+        <f t="shared" si="1"/>
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="R25" s="7">
+        <f t="shared" si="2"/>
+        <v>1.177</v>
       </c>
     </row>
   </sheetData>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-Picarro.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-Picarro.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7803C917-8512-4C15-835D-C9CB7E031BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76CCDDB3-1FAE-418A-81E3-6C79244AE491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -777,7 +777,7 @@
   <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" style="4" bestFit="1" customWidth="1"/>
